--- a/Пользователи для загрузки в ДО.xlsx
+++ b/Пользователи для загрузки в ДО.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60.5703125" customWidth="1" min="1" max="1"/>
@@ -482,6 +482,7 @@
     <col width="41.85546875" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" thickBot="1">
@@ -515,6 +516,11 @@
           <t>Главный бухгалтер</t>
         </is>
       </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\abdrazakova</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="inlineStr">
@@ -547,6 +553,11 @@
           <t>Начальник производства</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\badritdinov</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A3" s="1" t="inlineStr">
@@ -579,6 +590,11 @@
           <t>Технолог очистных сооружений</t>
         </is>
       </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\baybazarova</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" thickBot="1">
       <c r="A4" s="1" t="inlineStr">
@@ -611,6 +627,11 @@
           <t>Заместитель главного инженера</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\azat</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" thickBot="1">
       <c r="A5" s="1" t="inlineStr">
@@ -643,6 +664,11 @@
           <t>Оператор котельной 4 разряда</t>
         </is>
       </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\baranova</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="1" t="inlineStr">
@@ -675,6 +701,11 @@
           <t>Программист</t>
         </is>
       </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\basharov.n</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A7" s="1" t="inlineStr">
@@ -707,6 +738,11 @@
           <t>Инженер-электроник</t>
         </is>
       </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\beltukov</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A8" s="1" t="inlineStr">
@@ -739,6 +775,11 @@
           <t>Заместитель главного бухгалтера</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\bespalova</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="1" t="inlineStr">
@@ -771,6 +812,11 @@
           <t>Начальник очистных сооружений</t>
         </is>
       </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\bikkuzin</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickBot="1">
       <c r="A10" s="1" t="inlineStr">
@@ -803,6 +849,11 @@
           <t>Инженер-механик</t>
         </is>
       </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\birlev.a</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A11" s="1" t="inlineStr">
@@ -835,6 +886,11 @@
           <t>Бухгалтер</t>
         </is>
       </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\brovkina.n</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="1" t="inlineStr">
@@ -867,6 +923,11 @@
           <t>Специалист по охране труда</t>
         </is>
       </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\vtorova</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="A13" s="1" t="inlineStr">
@@ -899,6 +960,11 @@
           <t>Ведущий инженер-электроник</t>
         </is>
       </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\gafarov</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" thickBot="1">
       <c r="A14" s="1" t="inlineStr">
@@ -931,6 +997,11 @@
           <t>Системный администратор</t>
         </is>
       </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\gibadullin</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" thickBot="1">
       <c r="A15" s="1" t="inlineStr">
@@ -963,6 +1034,11 @@
           <t>Начальник отдела снабжения</t>
         </is>
       </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\np_oks2</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="A16" s="1" t="inlineStr">
@@ -995,6 +1071,11 @@
           <t>Специалист по охране труда</t>
         </is>
       </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\giniyatullin</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A17" s="1" t="inlineStr">
@@ -1027,6 +1108,11 @@
           <t>Главный инженер</t>
         </is>
       </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\zhamnov.v</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" thickBot="1">
       <c r="A18" s="1" t="inlineStr">
@@ -1059,6 +1145,11 @@
           <t>Мастер участка</t>
         </is>
       </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\nasosnaya</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="1" t="inlineStr">
@@ -1091,6 +1182,11 @@
           <t>Инженер-электроник</t>
         </is>
       </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\igonin.a</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="A20" s="1" t="inlineStr">
@@ -1123,6 +1219,11 @@
           <t>Мастер энергоцеха</t>
         </is>
       </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\kagirov</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="1" t="inlineStr">
@@ -1155,6 +1256,11 @@
           <t>Главный энергетик</t>
         </is>
       </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\kalenihin</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="1" t="inlineStr">
@@ -1187,6 +1293,11 @@
           <t>Программист</t>
         </is>
       </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\karamyshev</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" thickBot="1">
       <c r="A23" s="1" t="inlineStr">
@@ -1219,6 +1330,11 @@
           <t>Слесарь по контрольно-измерительным приборам и автоматике 5 разряда</t>
         </is>
       </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\karimovd</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A24" s="1" t="inlineStr">
@@ -1251,6 +1367,11 @@
           <t>Бухгалтер</t>
         </is>
       </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\kachurina</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" thickBot="1">
       <c r="A25" s="1" t="inlineStr">
@@ -1283,6 +1404,11 @@
           <t>Заместитель главного бухгалтера</t>
         </is>
       </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\kireeva</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" thickBot="1">
       <c r="A26" s="1" t="inlineStr">
@@ -1315,6 +1441,11 @@
           <t>Ведущий менеджер по закупкам</t>
         </is>
       </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\klusova</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
       <c r="A27" s="1" t="inlineStr">
@@ -1347,6 +1478,11 @@
           <t>Специалист по охране труда</t>
         </is>
       </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\kolesavin</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickBot="1">
       <c r="A28" s="1" t="inlineStr">
@@ -1379,6 +1515,7 @@
           <t>Директор по персоналу</t>
         </is>
       </c>
+      <c r="G28" s="2" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" thickBot="1">
       <c r="A29" s="1" t="inlineStr">
@@ -1411,6 +1548,11 @@
           <t>Главный бухгалтер</t>
         </is>
       </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\kotova</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" thickBot="1">
       <c r="A30" s="1" t="inlineStr">
@@ -1443,6 +1585,11 @@
           <t>Бухгалтер</t>
         </is>
       </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\krupinova</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" thickBot="1">
       <c r="A31" s="1" t="inlineStr">
@@ -1475,6 +1622,11 @@
           <t>Начальник участка по учету заработной платы</t>
         </is>
       </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\kunina</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" thickBot="1">
       <c r="A32" s="1" t="inlineStr">
@@ -1507,6 +1659,11 @@
           <t>Главный бухгалтер</t>
         </is>
       </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\lakushina</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" thickBot="1">
       <c r="A33" s="1" t="inlineStr">
@@ -1539,6 +1696,11 @@
           <t>Консультант 1С</t>
         </is>
       </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\loskunina</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" thickBot="1">
       <c r="A34" s="1" t="inlineStr">
@@ -1571,6 +1733,11 @@
           <t>Менеджер отдела снабжения</t>
         </is>
       </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\martyniuk</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" thickBot="1">
       <c r="A35" s="1" t="inlineStr">
@@ -1603,6 +1770,11 @@
           <t>Экономист-бухгалтер</t>
         </is>
       </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\meteykina</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" thickBot="1">
       <c r="A36" s="1" t="inlineStr">
@@ -1635,6 +1807,11 @@
           <t>Старший мастер смены</t>
         </is>
       </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\mingazhevl</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" thickBot="1">
       <c r="A37" s="1" t="inlineStr">
@@ -1663,6 +1840,11 @@
         </is>
       </c>
       <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\mirzin</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" thickBot="1">
       <c r="A38" s="1" t="inlineStr">
@@ -1695,6 +1877,11 @@
           <t>Главный инженер</t>
         </is>
       </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\mihaylik</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" thickBot="1">
       <c r="A39" s="1" t="inlineStr">
@@ -1727,6 +1914,11 @@
           <t>Главный механик</t>
         </is>
       </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\moryakov.a</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" thickBot="1">
       <c r="A40" s="1" t="inlineStr">
@@ -1759,6 +1951,11 @@
           <t>Главный энергетик</t>
         </is>
       </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\munirov</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" thickBot="1">
       <c r="A41" s="1" t="inlineStr">
@@ -1791,6 +1988,11 @@
           <t>Инженер по диагностике</t>
         </is>
       </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\nabiullin</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" thickBot="1">
       <c r="A42" s="1" t="inlineStr">
@@ -1823,6 +2025,11 @@
           <t>Начальник производства</t>
         </is>
       </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\anovikov</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" thickBot="1">
       <c r="A43" s="1" t="inlineStr">
@@ -1851,6 +2058,11 @@
         </is>
       </c>
       <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\novikova.i</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" thickBot="1">
       <c r="A44" s="1" t="inlineStr">
@@ -1883,6 +2095,11 @@
           <t>Начальник санитарно-промышленной лаборатории</t>
         </is>
       </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\nurgalieva</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" thickBot="1">
       <c r="A45" s="1" t="inlineStr">
@@ -1915,6 +2132,11 @@
           <t>Бухгалтер</t>
         </is>
       </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\kiubuh</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" thickBot="1">
       <c r="A46" s="1" t="inlineStr">
@@ -1943,6 +2165,11 @@
         </is>
       </c>
       <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\sakharov</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" thickBot="1">
       <c r="A47" s="1" t="inlineStr">
@@ -1975,6 +2202,11 @@
           <t>Главный энергетик</t>
         </is>
       </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\seregin.e</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" thickBot="1">
       <c r="A48" s="1" t="inlineStr">
@@ -2003,6 +2235,11 @@
         </is>
       </c>
       <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\skripko</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" thickBot="1">
       <c r="A49" s="1" t="inlineStr">
@@ -2035,6 +2272,11 @@
           <t>Менеджер</t>
         </is>
       </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\sorokina.e</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" thickBot="1">
       <c r="A50" s="1" t="inlineStr">
@@ -2067,6 +2309,11 @@
           <t>Бухгалтер</t>
         </is>
       </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\sorokina.l</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" thickBot="1">
       <c r="A51" s="1" t="inlineStr">
@@ -2099,6 +2346,11 @@
           <t>Начальник хозяйства</t>
         </is>
       </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\sudakov.v</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" thickBot="1">
       <c r="A52" s="1" t="inlineStr">
@@ -2131,6 +2383,11 @@
           <t>Бухгалтер по заработной плате</t>
         </is>
       </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\troshina.e</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" thickBot="1">
       <c r="A53" s="1" t="inlineStr">
@@ -2163,6 +2420,11 @@
           <t>Инженер-электроник</t>
         </is>
       </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\tyutin.i</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" thickBot="1">
       <c r="A54" s="1" t="inlineStr">
@@ -2195,6 +2457,11 @@
           <t>Менеджер отдела снабжения</t>
         </is>
       </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\fayzullina</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" thickBot="1">
       <c r="A55" s="1" t="inlineStr">
@@ -2227,6 +2494,11 @@
           <t>Главный инженер</t>
         </is>
       </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\filatov_a</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" thickBot="1">
       <c r="A56" s="1" t="inlineStr">
@@ -2259,6 +2531,11 @@
           <t>Начальник транспортно-складского хозяйства</t>
         </is>
       </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\haibullin</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" thickBot="1">
       <c r="A57" s="1" t="inlineStr">
@@ -2291,6 +2568,11 @@
           <t>Менеджер отдела снабжения</t>
         </is>
       </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\khayretdinov</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" thickBot="1">
       <c r="A58" s="1" t="inlineStr">
@@ -2323,6 +2605,11 @@
           <t>Механик</t>
         </is>
       </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\hamidullin</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" thickBot="1">
       <c r="A59" s="1" t="inlineStr">
@@ -2355,6 +2642,11 @@
           <t>Заместитель главного инженера в области качества и экологии</t>
         </is>
       </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\kachestvo</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" thickBot="1">
       <c r="A60" s="1" t="inlineStr">
@@ -2387,6 +2679,11 @@
           <t>Бухгалтер</t>
         </is>
       </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\hasanova</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" thickBot="1">
       <c r="A61" s="1" t="inlineStr">
@@ -2419,6 +2716,11 @@
           <t>Кладовщик материального склада</t>
         </is>
       </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\znpklad</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" thickBot="1">
       <c r="A62" s="1" t="inlineStr">
@@ -2451,6 +2753,11 @@
           <t>Ведущий бухгалтер по управленческому учету</t>
         </is>
       </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\roza</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" thickBot="1">
       <c r="A63" s="1" t="inlineStr">
@@ -2483,6 +2790,11 @@
           <t>Бухгалтер</t>
         </is>
       </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\shagargazina</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15.75" customHeight="1" thickBot="1">
       <c r="A64" s="1" t="inlineStr">
@@ -2515,6 +2827,11 @@
           <t>Резчик бумаги, картона и целлюлозы 4 разряда</t>
         </is>
       </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\shagimardanov</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" thickBot="1">
       <c r="A65" s="1" t="inlineStr">
@@ -2547,6 +2864,11 @@
           <t>Эколог</t>
         </is>
       </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>\\NEW_TN\shalaginova.i</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" thickBot="1">
       <c r="A66" s="1" t="inlineStr">
@@ -2579,6 +2901,11 @@
           <t>Инженер-химик</t>
         </is>
       </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\znpekolog</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" thickBot="1">
       <c r="A67" s="1" t="inlineStr">
@@ -2611,6 +2938,11 @@
           <t>Главный механик</t>
         </is>
       </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\znpmehanik</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" thickBot="1">
       <c r="A68" s="1" t="inlineStr">
@@ -2643,6 +2975,11 @@
           <t>Главный технолог</t>
         </is>
       </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\usupova</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" thickBot="1">
       <c r="A69" s="1" t="inlineStr">
@@ -2675,6 +3012,11 @@
           <t>Начальник энергоцеха</t>
         </is>
       </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\yalilov</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" thickBot="1">
       <c r="A70" s="1" t="inlineStr">
@@ -2705,6 +3047,11 @@
       <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Менеджер отдела снабжения</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>\\new_tn\yalilova</t>
         </is>
       </c>
     </row>
